--- a/tests/fixtures/clean_data.xlsx
+++ b/tests/fixtures/clean_data.xlsx
@@ -447,1102 +447,1102 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>44.98</v>
+        <v>2920</v>
       </c>
       <c r="B2" t="n">
-        <v>250.29</v>
+        <v>590</v>
       </c>
       <c r="C2" t="n">
-        <v>429.54</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68.03</v>
+        <v>580.2</v>
       </c>
       <c r="B3" t="n">
-        <v>217.06</v>
+        <v>531.2</v>
       </c>
       <c r="C3" t="n">
-        <v>505.84</v>
+        <v>5216.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59.28</v>
+        <v>8948.299999999999</v>
       </c>
       <c r="B4" t="n">
-        <v>230.45</v>
+        <v>4455.3</v>
       </c>
       <c r="C4" t="n">
-        <v>498.73</v>
+        <v>8686.299999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53.95</v>
+        <v>8287.4</v>
       </c>
       <c r="B5" t="n">
-        <v>156.72</v>
+        <v>8257.4</v>
       </c>
       <c r="C5" t="n">
-        <v>411.09</v>
+        <v>6468.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>36.24</v>
+        <v>1078.5</v>
       </c>
       <c r="B6" t="n">
-        <v>150.48</v>
+        <v>4432.5</v>
       </c>
       <c r="C6" t="n">
-        <v>499.26</v>
+        <v>2989.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36.25</v>
+        <v>635.6</v>
       </c>
       <c r="B7" t="n">
-        <v>234.56</v>
+        <v>7537.6</v>
       </c>
       <c r="C7" t="n">
-        <v>561.5</v>
+        <v>7695.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32.32</v>
+        <v>1560.7</v>
       </c>
       <c r="B8" t="n">
-        <v>179.14</v>
+        <v>1393.7</v>
       </c>
       <c r="C8" t="n">
-        <v>444.13</v>
+        <v>2809.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64.65000000000001</v>
+        <v>8661.799999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>204.93</v>
+        <v>4319.8</v>
       </c>
       <c r="C9" t="n">
-        <v>499.13</v>
+        <v>7648.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54.04</v>
+        <v>740.9</v>
       </c>
       <c r="B10" t="n">
-        <v>168.83</v>
+        <v>1294.9</v>
       </c>
       <c r="C10" t="n">
-        <v>504.13</v>
+        <v>4951.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58.32</v>
+        <v>7296.1</v>
       </c>
       <c r="B11" t="n">
-        <v>205.45</v>
+        <v>4005.1</v>
       </c>
       <c r="C11" t="n">
-        <v>456.18</v>
+        <v>1757.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30.82</v>
+        <v>4270</v>
       </c>
       <c r="B12" t="n">
-        <v>188.07</v>
+        <v>9090</v>
       </c>
       <c r="C12" t="n">
-        <v>552.97</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68.8</v>
+        <v>1705.3</v>
       </c>
       <c r="B13" t="n">
-        <v>225.82</v>
+        <v>6443.3</v>
       </c>
       <c r="C13" t="n">
-        <v>526.65</v>
+        <v>6414.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63.3</v>
+        <v>8872.4</v>
       </c>
       <c r="B14" t="n">
-        <v>240.4</v>
+        <v>2547.4</v>
       </c>
       <c r="C14" t="n">
-        <v>555.02</v>
+        <v>8714.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>38.49</v>
+        <v>4560.5</v>
       </c>
       <c r="B15" t="n">
-        <v>210.62</v>
+        <v>667.5</v>
       </c>
       <c r="C15" t="n">
-        <v>481.69</v>
+        <v>5126.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37.27</v>
+        <v>6232.6</v>
       </c>
       <c r="B16" t="n">
-        <v>175.54</v>
+        <v>5454.6</v>
       </c>
       <c r="C16" t="n">
-        <v>535.34</v>
+        <v>6884.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>37.34</v>
+        <v>3253.7</v>
       </c>
       <c r="B17" t="n">
-        <v>173.72</v>
+        <v>5410.7</v>
       </c>
       <c r="C17" t="n">
-        <v>510.93</v>
+        <v>8075.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>42.17</v>
+        <v>1394.8</v>
       </c>
       <c r="B18" t="n">
-        <v>224.67</v>
+        <v>8574.799999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>437.88</v>
+        <v>7751.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>50.99</v>
+        <v>1195.9</v>
       </c>
       <c r="B19" t="n">
-        <v>190.71</v>
+        <v>8228.9</v>
       </c>
       <c r="C19" t="n">
-        <v>432.57</v>
+        <v>5983.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47.28</v>
+        <v>8083.1</v>
       </c>
       <c r="B20" t="n">
-        <v>146.88</v>
+        <v>4815.1</v>
       </c>
       <c r="C20" t="n">
-        <v>515.75</v>
+        <v>744.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>41.65</v>
+        <v>1848.2</v>
       </c>
       <c r="B21" t="n">
-        <v>229.64</v>
+        <v>3268.2</v>
       </c>
       <c r="C21" t="n">
-        <v>435.16</v>
+        <v>1477.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>54.47</v>
+        <v>3040</v>
       </c>
       <c r="B22" t="n">
-        <v>194.28</v>
+        <v>4340</v>
       </c>
       <c r="C22" t="n">
-        <v>583.0700000000001</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.58</v>
+        <v>1559.4</v>
       </c>
       <c r="B23" t="n">
-        <v>161.09</v>
+        <v>4523.4</v>
       </c>
       <c r="C23" t="n">
-        <v>406.53</v>
+        <v>1893.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41.69</v>
+        <v>452.5</v>
       </c>
       <c r="B24" t="n">
-        <v>145.93</v>
+        <v>6007.5</v>
       </c>
       <c r="C24" t="n">
-        <v>516.76</v>
+        <v>6767.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>44.65</v>
+        <v>6375.6</v>
       </c>
       <c r="B25" t="n">
-        <v>175.1</v>
+        <v>8366.6</v>
       </c>
       <c r="C25" t="n">
-        <v>550.84</v>
+        <v>2755.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48.24</v>
+        <v>3117.7</v>
       </c>
       <c r="B26" t="n">
-        <v>148.02</v>
+        <v>6839.7</v>
       </c>
       <c r="C26" t="n">
-        <v>508.69</v>
+        <v>884.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61.41</v>
+        <v>7851.8</v>
       </c>
       <c r="B27" t="n">
-        <v>230.14</v>
+        <v>3670.8</v>
       </c>
       <c r="C27" t="n">
-        <v>496.46</v>
+        <v>4956.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37.99</v>
+        <v>5200.9</v>
       </c>
       <c r="B28" t="n">
-        <v>147.65</v>
+        <v>9433.9</v>
       </c>
       <c r="C28" t="n">
-        <v>414.89</v>
+        <v>8857.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>50.57</v>
+        <v>745.1</v>
       </c>
       <c r="B29" t="n">
-        <v>191.83</v>
+        <v>2596.1</v>
       </c>
       <c r="C29" t="n">
-        <v>498.39</v>
+        <v>560.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>53.7</v>
+        <v>2713.2</v>
       </c>
       <c r="B30" t="n">
-        <v>183.7</v>
+        <v>5419.2</v>
       </c>
       <c r="C30" t="n">
-        <v>445.48</v>
+        <v>9633.200000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31.86</v>
+        <v>9656.299999999999</v>
       </c>
       <c r="B31" t="n">
-        <v>158.24</v>
+        <v>7880.3</v>
       </c>
       <c r="C31" t="n">
-        <v>465.55</v>
+        <v>9176.299999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54.3</v>
+        <v>5420</v>
       </c>
       <c r="B32" t="n">
-        <v>205.61</v>
+        <v>8160</v>
       </c>
       <c r="C32" t="n">
-        <v>546.74</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>36.82</v>
+        <v>7712.5</v>
       </c>
       <c r="B33" t="n">
-        <v>193.2</v>
+        <v>9770.5</v>
       </c>
       <c r="C33" t="n">
-        <v>592.66</v>
+        <v>9415.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32.6</v>
+        <v>9868.6</v>
       </c>
       <c r="B34" t="n">
-        <v>144.33</v>
+        <v>7864.6</v>
       </c>
       <c r="C34" t="n">
-        <v>443.93</v>
+        <v>753.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67.95999999999999</v>
+        <v>1959.7</v>
       </c>
       <c r="B35" t="n">
-        <v>238.75</v>
+        <v>360.7</v>
       </c>
       <c r="C35" t="n">
-        <v>443.08</v>
+        <v>4823.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>68.63</v>
+        <v>9093.799999999999</v>
       </c>
       <c r="B36" t="n">
-        <v>172.8</v>
+        <v>2811.8</v>
       </c>
       <c r="C36" t="n">
-        <v>585.58</v>
+        <v>8706.799999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>62.34</v>
+        <v>1409.9</v>
       </c>
       <c r="B37" t="n">
-        <v>160.28</v>
+        <v>7097.9</v>
       </c>
       <c r="C37" t="n">
-        <v>499.02</v>
+        <v>6834.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42.18</v>
+        <v>7080.1</v>
       </c>
       <c r="B38" t="n">
-        <v>217.32</v>
+        <v>9170.1</v>
       </c>
       <c r="C38" t="n">
-        <v>529.36</v>
+        <v>8298.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33.91</v>
+        <v>6011.2</v>
       </c>
       <c r="B39" t="n">
-        <v>152.9</v>
+        <v>2576.2</v>
       </c>
       <c r="C39" t="n">
-        <v>428.57</v>
+        <v>6392.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>57.37</v>
+        <v>5227.3</v>
       </c>
       <c r="B40" t="n">
-        <v>182.39</v>
+        <v>4534.3</v>
       </c>
       <c r="C40" t="n">
-        <v>418.28</v>
+        <v>1434.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47.61</v>
+        <v>3886.4</v>
       </c>
       <c r="B41" t="n">
-        <v>186.28</v>
+        <v>2022.4</v>
       </c>
       <c r="C41" t="n">
-        <v>502.3</v>
+        <v>9882.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>34.88</v>
+        <v>9480</v>
       </c>
       <c r="B42" t="n">
-        <v>193.47</v>
+        <v>4200</v>
       </c>
       <c r="C42" t="n">
-        <v>414.42</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>49.81</v>
+        <v>7607.6</v>
       </c>
       <c r="B43" t="n">
-        <v>257.25</v>
+        <v>1689.6</v>
       </c>
       <c r="C43" t="n">
-        <v>553.9</v>
+        <v>8168.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>31.38</v>
+        <v>5924.7</v>
       </c>
       <c r="B44" t="n">
-        <v>227.53</v>
+        <v>1448.7</v>
       </c>
       <c r="C44" t="n">
-        <v>574.14</v>
+        <v>213.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66.37</v>
+        <v>4319.8</v>
       </c>
       <c r="B45" t="n">
-        <v>177.47</v>
+        <v>1519.8</v>
       </c>
       <c r="C45" t="n">
-        <v>417.69</v>
+        <v>1428.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40.35</v>
+        <v>1220.9</v>
       </c>
       <c r="B46" t="n">
-        <v>247.37</v>
+        <v>2732.9</v>
       </c>
       <c r="C46" t="n">
-        <v>414.07</v>
+        <v>4557.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56.5</v>
+        <v>6075.1</v>
       </c>
       <c r="B47" t="n">
-        <v>233.99</v>
+        <v>1003.1</v>
       </c>
       <c r="C47" t="n">
-        <v>496.48</v>
+        <v>1516.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>42.47</v>
+        <v>6625.2</v>
       </c>
       <c r="B48" t="n">
-        <v>171.44</v>
+        <v>1123.2</v>
       </c>
       <c r="C48" t="n">
-        <v>573.73</v>
+        <v>7562.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50.8</v>
+        <v>205.3</v>
       </c>
       <c r="B49" t="n">
-        <v>177.14</v>
+        <v>1347.3</v>
       </c>
       <c r="C49" t="n">
-        <v>502.52</v>
+        <v>2153.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51.87</v>
+        <v>3251.4</v>
       </c>
       <c r="B50" t="n">
-        <v>155.53</v>
+        <v>7832.4</v>
       </c>
       <c r="C50" t="n">
-        <v>536.6900000000001</v>
+        <v>4936.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37.39</v>
+        <v>884.5</v>
       </c>
       <c r="B51" t="n">
-        <v>190.66</v>
+        <v>3122.5</v>
       </c>
       <c r="C51" t="n">
-        <v>477.98</v>
+        <v>4345.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>68.78</v>
+        <v>4950</v>
       </c>
       <c r="B52" t="n">
-        <v>252.77</v>
+        <v>5260</v>
       </c>
       <c r="C52" t="n">
-        <v>502.82</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>61.01</v>
+        <v>4401.7</v>
       </c>
       <c r="B53" t="n">
-        <v>184.05</v>
+        <v>9472.700000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>519.67</v>
+        <v>2751.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67.58</v>
+        <v>9695.799999999999</v>
       </c>
       <c r="B54" t="n">
-        <v>192.17</v>
+        <v>637.8</v>
       </c>
       <c r="C54" t="n">
-        <v>583.52</v>
+        <v>3899.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>65.79000000000001</v>
+        <v>3308.9</v>
       </c>
       <c r="B55" t="n">
-        <v>250.05</v>
+        <v>7293.9</v>
       </c>
       <c r="C55" t="n">
-        <v>537.6900000000001</v>
+        <v>5141.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>53.92</v>
+        <v>5612.1</v>
       </c>
       <c r="B56" t="n">
-        <v>253.68</v>
+        <v>9385.1</v>
       </c>
       <c r="C56" t="n">
-        <v>577.15</v>
+        <v>6332.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66.87</v>
+        <v>7722.2</v>
       </c>
       <c r="B57" t="n">
-        <v>170.57</v>
+        <v>4225.2</v>
       </c>
       <c r="C57" t="n">
-        <v>455.03</v>
+        <v>5738.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>33.54</v>
+        <v>8631.299999999999</v>
       </c>
       <c r="B58" t="n">
-        <v>225.16</v>
+        <v>8936.299999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>575.62</v>
+        <v>5787.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>37.84</v>
+        <v>5142.4</v>
       </c>
       <c r="B59" t="n">
-        <v>146</v>
+        <v>119.4</v>
       </c>
       <c r="C59" t="n">
-        <v>581.36</v>
+        <v>5434.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>31.81</v>
+        <v>9218.5</v>
       </c>
       <c r="B60" t="n">
-        <v>156.17</v>
+        <v>493.5</v>
       </c>
       <c r="C60" t="n">
-        <v>593.16</v>
+        <v>720.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>43.01</v>
+        <v>1834.6</v>
       </c>
       <c r="B61" t="n">
-        <v>200.78</v>
+        <v>8947.6</v>
       </c>
       <c r="C61" t="n">
-        <v>565.96</v>
+        <v>4962.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>45.55</v>
+        <v>7310</v>
       </c>
       <c r="B62" t="n">
-        <v>210.69</v>
+        <v>4220</v>
       </c>
       <c r="C62" t="n">
-        <v>574.29</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>40.85</v>
+        <v>8021.8</v>
       </c>
       <c r="B63" t="n">
-        <v>179.23</v>
+        <v>3641.8</v>
       </c>
       <c r="C63" t="n">
-        <v>430.32</v>
+        <v>326.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63.15</v>
+        <v>4722.9</v>
       </c>
       <c r="B64" t="n">
-        <v>157.38</v>
+        <v>7151.9</v>
       </c>
       <c r="C64" t="n">
-        <v>524.61</v>
+        <v>4688.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44.27</v>
+        <v>2912.1</v>
       </c>
       <c r="B65" t="n">
-        <v>170.92</v>
+        <v>5884.1</v>
       </c>
       <c r="C65" t="n">
-        <v>491.14</v>
+        <v>554.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>41.24</v>
+        <v>3109.2</v>
       </c>
       <c r="B66" t="n">
-        <v>242.89</v>
+        <v>9044.200000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>440.41</v>
+        <v>3147.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>51.71</v>
+        <v>6842.3</v>
       </c>
       <c r="B67" t="n">
-        <v>222.08</v>
+        <v>5065.3</v>
       </c>
       <c r="C67" t="n">
-        <v>527.86</v>
+        <v>1628.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>35.64</v>
+        <v>650.4</v>
       </c>
       <c r="B68" t="n">
-        <v>259.84</v>
+        <v>3094.4</v>
       </c>
       <c r="C68" t="n">
-        <v>404.26</v>
+        <v>8781.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>62.09</v>
+        <v>8324.5</v>
       </c>
       <c r="B69" t="n">
-        <v>178.33</v>
+        <v>7511.5</v>
       </c>
       <c r="C69" t="n">
-        <v>493.77</v>
+        <v>6230.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>32.98</v>
+        <v>254.6</v>
       </c>
       <c r="B70" t="n">
-        <v>194.41</v>
+        <v>8676.6</v>
       </c>
       <c r="C70" t="n">
-        <v>459.8</v>
+        <v>370.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>69.48</v>
+        <v>7132.7</v>
       </c>
       <c r="B71" t="n">
-        <v>244.11</v>
+        <v>3261.7</v>
       </c>
       <c r="C71" t="n">
-        <v>597.66</v>
+        <v>2020.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>60.89</v>
+        <v>1980</v>
       </c>
       <c r="B72" t="n">
-        <v>216.62</v>
+        <v>6380</v>
       </c>
       <c r="C72" t="n">
-        <v>411.2</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>37.95</v>
+        <v>55.9</v>
       </c>
       <c r="B73" t="n">
-        <v>179.83</v>
+        <v>9191.9</v>
       </c>
       <c r="C73" t="n">
-        <v>514.76</v>
+        <v>5115.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>30.22</v>
+        <v>7290.1</v>
       </c>
       <c r="B74" t="n">
-        <v>205.04</v>
+        <v>873.1</v>
       </c>
       <c r="C74" t="n">
-        <v>544.97</v>
+        <v>4689.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>62.62</v>
+        <v>7751.2</v>
       </c>
       <c r="B75" t="n">
-        <v>153.48</v>
+        <v>3857.2</v>
       </c>
       <c r="C75" t="n">
-        <v>579.0700000000001</v>
+        <v>630.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>58.27</v>
+        <v>2587.3</v>
       </c>
       <c r="B76" t="n">
-        <v>237.98</v>
+        <v>3318.3</v>
       </c>
       <c r="C76" t="n">
-        <v>486.91</v>
+        <v>2206.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>59.16</v>
+        <v>3663.4</v>
       </c>
       <c r="B77" t="n">
-        <v>166.51</v>
+        <v>2620.4</v>
       </c>
       <c r="C77" t="n">
-        <v>493.79</v>
+        <v>5291.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>60.85</v>
+        <v>7709.5</v>
       </c>
       <c r="B78" t="n">
-        <v>201.8</v>
+        <v>2924.5</v>
       </c>
       <c r="C78" t="n">
-        <v>563.37</v>
+        <v>4823.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>32.96</v>
+        <v>8154.6</v>
       </c>
       <c r="B79" t="n">
-        <v>203.13</v>
+        <v>9986.6</v>
       </c>
       <c r="C79" t="n">
-        <v>439.54</v>
+        <v>6951.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>44.34</v>
+        <v>464.7</v>
       </c>
       <c r="B80" t="n">
-        <v>173.25</v>
+        <v>2402.7</v>
       </c>
       <c r="C80" t="n">
-        <v>588.3</v>
+        <v>5546.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>34.63</v>
+        <v>5247.8</v>
       </c>
       <c r="B81" t="n">
-        <v>248.53</v>
+        <v>499.8</v>
       </c>
       <c r="C81" t="n">
-        <v>504.32</v>
+        <v>7248.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>64.52</v>
+        <v>5970</v>
       </c>
       <c r="B82" t="n">
-        <v>190.45</v>
+        <v>2200</v>
       </c>
       <c r="C82" t="n">
-        <v>462.95</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>54.93</v>
+        <v>3745.1</v>
       </c>
       <c r="B83" t="n">
-        <v>253.88</v>
+        <v>1757.1</v>
       </c>
       <c r="C83" t="n">
-        <v>467.68</v>
+        <v>8710.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>43.24</v>
+        <v>3567.2</v>
       </c>
       <c r="B84" t="n">
-        <v>234.38</v>
+        <v>5890.2</v>
       </c>
       <c r="C84" t="n">
-        <v>568</v>
+        <v>9323.200000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>32.54</v>
+        <v>6118.3</v>
       </c>
       <c r="B85" t="n">
-        <v>197.79</v>
+        <v>573.3</v>
       </c>
       <c r="C85" t="n">
-        <v>428.68</v>
+        <v>8772.299999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>42.44</v>
+        <v>1996.4</v>
       </c>
       <c r="B86" t="n">
-        <v>141.43</v>
+        <v>7055.4</v>
       </c>
       <c r="C86" t="n">
-        <v>574.21</v>
+        <v>2274.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>43.02</v>
+        <v>5467.5</v>
       </c>
       <c r="B87" t="n">
-        <v>147.17</v>
+        <v>7470.5</v>
       </c>
       <c r="C87" t="n">
-        <v>575.46</v>
+        <v>8400.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>59.18</v>
+        <v>7068.6</v>
       </c>
       <c r="B88" t="n">
-        <v>239.09</v>
+        <v>4046.6</v>
       </c>
       <c r="C88" t="n">
-        <v>444.48</v>
+        <v>7631.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>55.5</v>
+        <v>2809.7</v>
       </c>
       <c r="B89" t="n">
-        <v>188.56</v>
+        <v>9490.700000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>539.03</v>
+        <v>5206.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>65.48999999999999</v>
+        <v>976.8</v>
       </c>
       <c r="B90" t="n">
-        <v>146.38</v>
+        <v>5467.8</v>
       </c>
       <c r="C90" t="n">
-        <v>479.66</v>
+        <v>9658.799999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>48.89</v>
+        <v>3046.9</v>
       </c>
       <c r="B91" t="n">
-        <v>171.16</v>
+        <v>7453.9</v>
       </c>
       <c r="C91" t="n">
-        <v>423.48</v>
+        <v>3983.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>34.78</v>
+        <v>2120</v>
       </c>
       <c r="B92" t="n">
-        <v>173.74</v>
+        <v>3530</v>
       </c>
       <c r="C92" t="n">
-        <v>552.62</v>
+        <v>8950</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>58.53</v>
+        <v>3584.2</v>
       </c>
       <c r="B93" t="n">
-        <v>253.2</v>
+        <v>5149.2</v>
       </c>
       <c r="C93" t="n">
-        <v>433.34</v>
+        <v>9279.200000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>60.43</v>
+        <v>1158.3</v>
       </c>
       <c r="B94" t="n">
-        <v>247.24</v>
+        <v>2770.3</v>
       </c>
       <c r="C94" t="n">
-        <v>407.4</v>
+        <v>703.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>52.45</v>
+        <v>1818.4</v>
       </c>
       <c r="B95" t="n">
-        <v>164.27</v>
+        <v>2810.4</v>
       </c>
       <c r="C95" t="n">
-        <v>455.12</v>
+        <v>4919.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>60.84</v>
+        <v>9394.5</v>
       </c>
       <c r="B96" t="n">
-        <v>152.04</v>
+        <v>2961.5</v>
       </c>
       <c r="C96" t="n">
-        <v>415.06</v>
+        <v>3384.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>49.75</v>
+        <v>343.6</v>
       </c>
       <c r="B97" t="n">
-        <v>208.77</v>
+        <v>3194.6</v>
       </c>
       <c r="C97" t="n">
-        <v>463.41</v>
+        <v>9067.6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>50.91</v>
+        <v>9699.700000000001</v>
       </c>
       <c r="B98" t="n">
-        <v>229.45</v>
+        <v>1075.7</v>
       </c>
       <c r="C98" t="n">
-        <v>528.3</v>
+        <v>913.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>47.1</v>
+        <v>4937.8</v>
       </c>
       <c r="B99" t="n">
-        <v>212.09</v>
+        <v>5730.8</v>
       </c>
       <c r="C99" t="n">
-        <v>586.48</v>
+        <v>2224.8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>31.02</v>
+        <v>9507.9</v>
       </c>
       <c r="B100" t="n">
-        <v>249.11</v>
+        <v>9397.9</v>
       </c>
       <c r="C100" t="n">
-        <v>412.61</v>
+        <v>4084.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>34.32</v>
+        <v>5986.1</v>
       </c>
       <c r="B101" t="n">
-        <v>252.63</v>
+        <v>6421.1</v>
       </c>
       <c r="C101" t="n">
-        <v>551.26</v>
+        <v>5838.1</v>
       </c>
     </row>
   </sheetData>
